--- a/_projet/Criterios-evaluation.xlsx
+++ b/_projet/Criterios-evaluation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/FabioCruz/Documents/01-Projects/ENSGSI/CI3/_projet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A764CD0E-C786-4A46-B426-67887489B017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075DED92-2ED2-DA43-B960-821607E10EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,10 +109,10 @@
     <t>Originalité et Frugalité (6 points)</t>
   </si>
   <si>
-    <t xml:space="preserve">Le mécanisme est inscrit dans une surface de 30 x 30 cm, sans la dépasser verticalement. </t>
-  </si>
-  <si>
     <t>Usage cohérent des composants électroniques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le mécanisme est inscrit dans une surface de 200 x 200 mm, sans la dépasser verticalement. </t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -710,7 +710,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>0</v>
